--- a/data/jlcpcb_bom.xlsx
+++ b/data/jlcpcb_bom.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,22 +441,18 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>100K</t>
+          <t>-5V</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0603</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>R5</t>
-        </is>
-      </c>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>R16</t>
+          <t>PS1</t>
         </is>
       </c>
     </row>
@@ -468,38 +464,42 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0805</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>R11</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>R22</t>
+          <t>R6, R8</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>100n</t>
+          <t>100K</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0603</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>C23</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>R21</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>100p</t>
+          <t>100n</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -509,12 +509,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>C5, C8</t>
+          <t>C4, C8</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>C12, C24</t>
+          <t>C19</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>C13, C19</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -539,25 +539,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>100uH</t>
+          <t>10K</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0805</t>
+          <t>0603</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>L1, L4</t>
+          <t>R17, R25</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>10n</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -567,19 +567,15 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>R6, R13, R25, R27</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>R18, R19, R29</t>
-        </is>
-      </c>
+          <t>C16</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>10n</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -589,19 +585,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>C7, C12</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>R10, R14</t>
+          <t>C22, C24</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10n</t>
+          <t>10p</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -609,21 +605,17 @@
           <t>0603</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>C16, C25</t>
-        </is>
-      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>C1, C9</t>
+          <t>C3, C14</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10n</t>
+          <t>10p</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -633,19 +625,15 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>C29</t>
-        </is>
-      </c>
+          <t>C17</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10p</t>
+          <t>10uH</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -653,21 +641,17 @@
           <t>0603</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>C10</t>
-        </is>
-      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>C4, C21</t>
+          <t>L5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10p</t>
+          <t>10uH</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -677,19 +661,15 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>C28, C30</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>C14, C15</t>
-        </is>
-      </c>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10uH</t>
+          <t>1K</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -699,19 +679,15 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>L3</t>
-        </is>
-      </c>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>12V</t>
+          <t>1u</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -721,153 +697,157 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>PS3</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>C15</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>C21</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1K</t>
+          <t>1uH</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0603</t>
+          <t>0805</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>R8</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>R20</t>
-        </is>
-      </c>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1K</t>
+          <t>2200n</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0805</t>
+          <t>0603</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>R7, R21, R24</t>
+          <t>C27</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1u</t>
+          <t>2200n</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0603</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>C7</t>
-        </is>
-      </c>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>C17</t>
+          <t>C2, C6, C29</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1u</t>
+          <t>220n</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0805</t>
+          <t>0603</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>C18</t>
+          <t>C10</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>C20, C27</t>
+          <t>C23, C25, C26</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1uH</t>
+          <t>470</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0805</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>L5</t>
-        </is>
-      </c>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>R23</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2200n</t>
+          <t>470</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0603</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>R20</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>C6, C11</t>
+          <t>R14</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2200n</t>
+          <t>4K7</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0805</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>R4, R16</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>R7, R22</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>220n</t>
+          <t>4K7</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -877,7 +857,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>C22, C26</t>
+          <t>R18</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -885,7 +865,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>500</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -893,17 +873,21 @@
           <t>0603</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>R3, R5, R10, R24, R27</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R29</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>500</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -914,14 +898,14 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>R3, R17, R26</t>
+          <t>R13, R15</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>4K7</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -931,7 +915,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>R12, R15</t>
+          <t>R26</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -939,7 +923,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>4K7</t>
+          <t>5K</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -949,104 +933,10 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>R23</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>R11</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>0603</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>0805</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>R9, R30</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>5K</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>0805</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
           <t>R28</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>5V</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>0603</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>PS1</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>9V</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>0603</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>PS2</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jlcpcb_bom.xlsx
+++ b/data/jlcpcb_bom.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>-5V</t>
+          <t>100K</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -452,14 +452,14 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PS1</t>
+          <t>R4</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>100K</t>
+          <t>100n</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -469,19 +469,15 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>R11</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>R6, R8</t>
-        </is>
-      </c>
+          <t>C26</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>100K</t>
+          <t>100n</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -489,17 +485,17 @@
           <t>0805</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>R21</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>C18</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>100n</t>
+          <t>100p</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -509,19 +505,15 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>C4, C8</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>C19</t>
-        </is>
-      </c>
+          <t>C5, C9</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>100p</t>
+          <t>100uH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -531,7 +523,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -544,13 +536,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0603</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>R28</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>R17, R25</t>
+          <t>R2</t>
         </is>
       </c>
     </row>
@@ -567,15 +563,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>C16</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>C19, C22</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>C21</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10n</t>
+          <t>10p</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -585,91 +585,99 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>C7, C12</t>
+          <t>C14</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>C22, C24</t>
+          <t>C28</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10p</t>
+          <t>10uH</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0603</t>
+          <t>0805</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>C3, C14</t>
+          <t>L2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10p</t>
+          <t>1K</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0805</t>
+          <t>0603</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>C17</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>R8, R13, R27</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10uH</t>
+          <t>1K</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0603</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>R10</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>L5</t>
+          <t>R17, R22</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10uH</t>
+          <t>1u</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0805</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1K</t>
+          <t>1u</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -677,52 +685,52 @@
           <t>0805</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>C1, C7</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1u</t>
+          <t>1uH</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0603</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>C15</t>
-        </is>
-      </c>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>C21</t>
+          <t>L1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1uH</t>
+          <t>2200n</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0805</t>
+          <t>0603</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>L3</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>C3, C16</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -732,20 +740,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0603</t>
+          <t>0805</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>C27</t>
+          <t>C23, C25</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2200n</t>
+          <t>220n</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -753,17 +761,21 @@
           <t>0805</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>C11</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>C2, C6, C29</t>
+          <t>C27</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>220n</t>
+          <t>470</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -771,14 +783,10 @@
           <t>0603</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>C10</t>
-        </is>
-      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>C23, C25, C26</t>
+          <t>R16, R26</t>
         </is>
       </c>
     </row>
@@ -790,12 +798,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0603</t>
+          <t>0805</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>R23</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -803,24 +811,20 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>4K7</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0805</t>
+          <t>0603</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>R20</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
           <t>R14</t>
         </is>
       </c>
+      <c r="D21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -830,113 +834,15 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0603</t>
+          <t>0805</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>R4, R16</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>R7, R22</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>4K7</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>0805</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
           <t>R18</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>0603</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>R3, R5, R10, R24, R27</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>R29</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>0805</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>R13, R15</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>5K</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>0603</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>R26</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>5K</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>0805</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>R28</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jlcpcb_bom.xlsx
+++ b/data/jlcpcb_bom.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,18 +441,18 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>100K</t>
+          <t>-12V</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0805</t>
+          <t>0603</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>PS1</t>
         </is>
       </c>
     </row>
@@ -467,71 +467,79 @@
           <t>0603</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>C26</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>C22</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>100n</t>
+          <t>10K</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0805</t>
+          <t>0603</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>C18</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>R16</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>R18</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>100p</t>
+          <t>10K</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0603</t>
+          <t>0805</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>C5, C9</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>R5, R15, R20</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>R27</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>100uH</t>
+          <t>10p</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0805</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>L3</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>C13</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>10p</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -539,43 +547,35 @@
           <t>0805</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>R28</t>
-        </is>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>C19</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10n</t>
+          <t>1K</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0603</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>C19, C22</t>
-        </is>
-      </c>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>C21</t>
+          <t>R6</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10p</t>
+          <t>1u</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -585,19 +585,15 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>C14</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>C28</t>
-        </is>
-      </c>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10uH</t>
+          <t>2200n</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -605,244 +601,66 @@
           <t>0805</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>C26</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1K</t>
+          <t>470</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0603</t>
+          <t>0805</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>R8, R13, R27</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>R5</t>
-        </is>
-      </c>
+          <t>R14</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1K</t>
+          <t>500</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0805</t>
+          <t>0603</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>R10</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>R17, R22</t>
-        </is>
-      </c>
+          <t>R26</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1u</t>
+          <t>500</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0603</t>
+          <t>0805</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>C6</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>1u</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>0805</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>C1, C7</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>1uH</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>0805</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2200n</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>0603</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>C3, C16</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2200n</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>0805</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>C23, C25</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>220n</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0805</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>C11</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>C27</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>470</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0603</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>R16, R26</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>470</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>0805</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>4K7</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>0603</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>R14</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>4K7</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>0805</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>R18</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>R23</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/jlcpcb_bom.xlsx
+++ b/data/jlcpcb_bom.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>-12V</t>
+          <t>100K</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -449,35 +449,39 @@
           <t>0603</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>PS1</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>R10, R14, R29</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>100n</t>
+          <t>100K</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0603</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>R30</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>C22</t>
+          <t>R5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>100n</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -487,19 +491,15 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>R16</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>R18</t>
-        </is>
-      </c>
+          <t>C13</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>100n</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -507,21 +507,17 @@
           <t>0805</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>R5, R15, R20</t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>R27</t>
+          <t>C18</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10p</t>
+          <t>100p</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -529,17 +525,17 @@
           <t>0603</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>C13</t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>C23</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10p</t>
+          <t>100p</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -550,50 +546,54 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>C19</t>
+          <t>C2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1K</t>
+          <t>100uH</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0805</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>R6</t>
-        </is>
-      </c>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>L5</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1u</t>
+          <t>10K</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0805</t>
+          <t>0603</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>R22</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2200n</t>
+          <t>10K</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -603,62 +603,396 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>C26</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>R19</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>10n</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0805</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>R14</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>C17, C20</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>10n</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0603</t>
+          <t>0805</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>R26</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>C19</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>C26, C28</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>10p</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0805</t>
+          <t>0603</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>R23</t>
+          <t>C12, C15, C30</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>10p</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>10uH</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>R12, R27</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>R1, R7</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>R15</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1u</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1uH</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2200n</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>C8, C16, C27</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2200n</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>C5, C22</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>220n</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>C25</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>4K7</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>R11</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>4K7</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>R18</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>R3, R13, R23, R25</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>5K</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>R17, R24</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>R16</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>5K</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>R20, R28</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>R21</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>9V</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>PS3</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>9V</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>PS1, PS2</t>
         </is>
       </c>
     </row>
